--- a/NEW BOT 02/Fan_Spare_Parts_Stock_Summary.xlsx
+++ b/NEW BOT 02/Fan_Spare_Parts_Stock_Summary.xlsx
@@ -652,7 +652,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Workflow: Warehouse -&gt; Report -&gt; Warehouse Reports -&gt; Report 3224  |  Company: FAN  |  Date Range: 2026-09-01 to 2026-09-19 (Running Date)</t>
+          <t>Workflow: Warehouse -&gt; Report -&gt; Warehouse Reports -&gt; Report 3224  |  Company: FAN  |  Date Range: 2026-09-01 to 2026-09-21 (Running Date)</t>
         </is>
       </c>
     </row>
@@ -662,18 +662,18 @@
       </c>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="5" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>4,385.05 Pcs</t>
+          <t>3,665.05 Pcs</t>
         </is>
       </c>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>BDT 4,588,920.91</t>
+          <t>BDT 4,331,949.74</t>
         </is>
       </c>
       <c r="I5" s="4" t="n"/>
@@ -713,7 +713,7 @@
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>331 Zero Stock Items</t>
+          <t>334 Zero Stock Items</t>
         </is>
       </c>
       <c r="E7" s="4" t="n"/>
@@ -782,14 +782,14 @@
         <v>12</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>43.23</v>
+        <v>35.23</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>195568.8468003</v>
+        <v>111021.63408146</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
     </row>
@@ -803,17 +803,17 @@
         <v>467</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>4341.82</v>
+        <v>3629.82</v>
       </c>
       <c r="F12" s="17" t="n">
-        <v>4393352.063385737</v>
+        <v>4220928.104245616</v>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>97.4%</t>
         </is>
       </c>
     </row>
@@ -3963,19 +3963,19 @@
         </is>
       </c>
       <c r="G68" s="23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H68" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I68" s="23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J68" s="23" t="n">
         <v>10057.8675</v>
       </c>
       <c r="K68" s="23" t="n">
-        <v>60347.204784</v>
+        <v>20115.734928</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -4010,19 +4010,19 @@
         </is>
       </c>
       <c r="G69" s="26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H69" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J69" s="26" t="n">
         <v>11078.9357</v>
       </c>
       <c r="K69" s="26" t="n">
-        <v>66473.61429426</v>
+        <v>22157.87143142</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -4621,19 +4621,19 @@
         </is>
       </c>
       <c r="G82" s="23" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H82" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I82" s="23" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J82" s="23" t="n">
         <v>325.8574</v>
       </c>
       <c r="K82" s="23" t="n">
-        <v>2932.7165217</v>
+        <v>977.5721739000001</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -4668,19 +4668,19 @@
         </is>
       </c>
       <c r="G83" s="26" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="H83" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I83" s="26" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J83" s="26" t="n">
         <v>16.2056</v>
       </c>
       <c r="K83" s="26" t="n">
-        <v>518.57915776</v>
+        <v>324.1119736</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -7958,19 +7958,19 @@
         </is>
       </c>
       <c r="G153" s="26" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H153" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I153" s="26" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J153" s="26" t="n">
         <v>15.26</v>
       </c>
       <c r="K153" s="26" t="n">
-        <v>732.48</v>
+        <v>717.22</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -10637,19 +10637,19 @@
         </is>
       </c>
       <c r="G210" s="23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H210" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I210" s="23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J210" s="23" t="n">
         <v>75.9393</v>
       </c>
       <c r="K210" s="23" t="n">
-        <v>531.57520003</v>
+        <v>379.69657145</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
@@ -13081,19 +13081,19 @@
         </is>
       </c>
       <c r="G262" s="23" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H262" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I262" s="23" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="J262" s="23" t="n">
         <v>46.9464</v>
       </c>
       <c r="K262" s="23" t="n">
-        <v>3755.7127328</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -14773,19 +14773,19 @@
         </is>
       </c>
       <c r="G298" s="23" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H298" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I298" s="23" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="J298" s="23" t="n">
         <v>26.18</v>
       </c>
       <c r="K298" s="23" t="n">
-        <v>15708</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299" ht="20" customHeight="1">
@@ -15807,19 +15807,19 @@
         </is>
       </c>
       <c r="G320" s="23" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H320" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I320" s="23" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J320" s="23" t="n">
         <v>247.735</v>
       </c>
       <c r="K320" s="23" t="n">
-        <v>2725.08480244</v>
+        <v>1981.87985632</v>
       </c>
     </row>
     <row r="321" ht="20" customHeight="1">
@@ -18956,19 +18956,19 @@
         </is>
       </c>
       <c r="G387" s="26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H387" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I387" s="26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J387" s="26" t="n">
         <v>21.05</v>
       </c>
       <c r="K387" s="26" t="n">
-        <v>147.35</v>
+        <v>105.25</v>
       </c>
     </row>
     <row r="388" ht="20" customHeight="1">
@@ -25395,19 +25395,19 @@
         </is>
       </c>
       <c r="G524" s="23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H524" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I524" s="23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J524" s="23" t="n">
         <v>3110.8278</v>
       </c>
       <c r="K524" s="23" t="n">
-        <v>18664.966956</v>
+        <v>12443.311304</v>
       </c>
     </row>
     <row r="525" ht="20" customHeight="1">
@@ -25489,19 +25489,19 @@
         </is>
       </c>
       <c r="G526" s="23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H526" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I526" s="23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J526" s="23" t="n">
         <v>69993.7061</v>
       </c>
       <c r="K526" s="23" t="n">
-        <v>279974.824364</v>
+        <v>139987.412182</v>
       </c>
     </row>
     <row r="527" ht="20" customHeight="1">
@@ -25583,19 +25583,19 @@
         </is>
       </c>
       <c r="G528" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H528" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I528" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J528" s="23" t="n">
         <v>1824.5617</v>
       </c>
       <c r="K528" s="23" t="n">
-        <v>3649.12346666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="529" ht="20" customHeight="1">
@@ -25945,11 +25945,11 @@
       <c r="G536" s="27" t="n"/>
       <c r="H536" s="27" t="n"/>
       <c r="I536" s="28" t="n">
-        <v>4385.05</v>
+        <v>3665.05</v>
       </c>
       <c r="J536" s="27" t="n"/>
       <c r="K536" s="28" t="n">
-        <v>4588920.910186038</v>
+        <v>4331949.738327078</v>
       </c>
     </row>
   </sheetData>
@@ -25966,7 +25966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K205"/>
+  <dimension ref="A1:K202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -26548,19 +26548,19 @@
         </is>
       </c>
       <c r="G14" s="23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H14" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J14" s="23" t="n">
         <v>10057.8675</v>
       </c>
       <c r="K14" s="23" t="n">
-        <v>60347.204784</v>
+        <v>20115.734928</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -26595,19 +26595,19 @@
         </is>
       </c>
       <c r="G15" s="26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H15" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J15" s="26" t="n">
         <v>11078.9357</v>
       </c>
       <c r="K15" s="26" t="n">
-        <v>66473.61429426</v>
+        <v>22157.87143142</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -27159,19 +27159,19 @@
         </is>
       </c>
       <c r="G27" s="26" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H27" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="26" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J27" s="26" t="n">
         <v>325.8574</v>
       </c>
       <c r="K27" s="26" t="n">
-        <v>2932.7165217</v>
+        <v>977.5721739000001</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -27206,19 +27206,19 @@
         </is>
       </c>
       <c r="G28" s="23" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="H28" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="23" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J28" s="23" t="n">
         <v>16.2056</v>
       </c>
       <c r="K28" s="23" t="n">
-        <v>518.57915776</v>
+        <v>324.1119736</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -29650,19 +29650,19 @@
         </is>
       </c>
       <c r="G80" s="23" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H80" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I80" s="23" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J80" s="23" t="n">
         <v>15.26</v>
       </c>
       <c r="K80" s="23" t="n">
-        <v>732.48</v>
+        <v>717.22</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -30966,19 +30966,19 @@
         </is>
       </c>
       <c r="G108" s="23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H108" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I108" s="23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J108" s="23" t="n">
         <v>75.9393</v>
       </c>
       <c r="K108" s="23" t="n">
-        <v>531.57520003</v>
+        <v>379.69657145</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -31736,22 +31736,22 @@
     <row r="125" ht="20" customHeight="1">
       <c r="A125" s="24" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>261</t>
         </is>
       </c>
       <c r="B125" s="24" t="inlineStr">
         <is>
-          <t>400200606</t>
+          <t>400200612</t>
         </is>
       </c>
       <c r="C125" s="24" t="inlineStr">
         <is>
-          <t>60598</t>
+          <t>60604</t>
         </is>
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>MS angle 1 Inch</t>
+          <t>MS Flat bar 1 Inch</t>
         </is>
       </c>
       <c r="E125" s="25" t="inlineStr">
@@ -31761,44 +31761,44 @@
       </c>
       <c r="F125" s="24" t="inlineStr">
         <is>
-          <t>Feet</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G125" s="26" t="n">
-        <v>80</v>
+        <v>3.3</v>
       </c>
       <c r="H125" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I125" s="26" t="n">
-        <v>80</v>
+        <v>3.3</v>
       </c>
       <c r="J125" s="26" t="n">
-        <v>46.9464</v>
+        <v>85.9071</v>
       </c>
       <c r="K125" s="26" t="n">
-        <v>3755.7127328</v>
+        <v>283.493419836</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="21" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>263</t>
         </is>
       </c>
       <c r="B126" s="21" t="inlineStr">
         <is>
-          <t>400200612</t>
+          <t>400200623</t>
         </is>
       </c>
       <c r="C126" s="21" t="inlineStr">
         <is>
-          <t>60604</t>
+          <t>60615</t>
         </is>
       </c>
       <c r="D126" s="22" t="inlineStr">
         <is>
-          <t>MS Flat bar 1 Inch</t>
+          <t>MS Pipe 1 Inch</t>
         </is>
       </c>
       <c r="E126" s="22" t="inlineStr">
@@ -31808,44 +31808,44 @@
       </c>
       <c r="F126" s="21" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>Feet</t>
         </is>
       </c>
       <c r="G126" s="23" t="n">
-        <v>3.3</v>
+        <v>80</v>
       </c>
       <c r="H126" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I126" s="23" t="n">
-        <v>3.3</v>
+        <v>80</v>
       </c>
       <c r="J126" s="23" t="n">
-        <v>85.9071</v>
+        <v>92.63160000000001</v>
       </c>
       <c r="K126" s="23" t="n">
-        <v>283.493419836</v>
+        <v>7410.526376</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="24" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>268</t>
         </is>
       </c>
       <c r="B127" s="24" t="inlineStr">
         <is>
-          <t>400200623</t>
+          <t>400200649</t>
         </is>
       </c>
       <c r="C127" s="24" t="inlineStr">
         <is>
-          <t>60615</t>
+          <t>60641</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>MS Pipe 1 Inch</t>
+          <t>Pneumatic nipple 8mm</t>
         </is>
       </c>
       <c r="E127" s="25" t="inlineStr">
@@ -31855,44 +31855,44 @@
       </c>
       <c r="F127" s="24" t="inlineStr">
         <is>
-          <t>Feet</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G127" s="26" t="n">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="H127" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I127" s="26" t="n">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="J127" s="26" t="n">
-        <v>92.63160000000001</v>
+        <v>36.84</v>
       </c>
       <c r="K127" s="26" t="n">
-        <v>7410.526376</v>
+        <v>221.04</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="21" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>269</t>
         </is>
       </c>
       <c r="B128" s="21" t="inlineStr">
         <is>
-          <t>400200649</t>
+          <t>400200650</t>
         </is>
       </c>
       <c r="C128" s="21" t="inlineStr">
         <is>
-          <t>60641</t>
+          <t>60642</t>
         </is>
       </c>
       <c r="D128" s="22" t="inlineStr">
         <is>
-          <t>Pneumatic nipple 8mm</t>
+          <t>Pneumatic nipple 10mm</t>
         </is>
       </c>
       <c r="E128" s="22" t="inlineStr">
@@ -31915,31 +31915,31 @@
         <v>6</v>
       </c>
       <c r="J128" s="23" t="n">
-        <v>36.84</v>
+        <v>42.1</v>
       </c>
       <c r="K128" s="23" t="n">
-        <v>221.04</v>
+        <v>252.6</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="24" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>270</t>
         </is>
       </c>
       <c r="B129" s="24" t="inlineStr">
         <is>
-          <t>400200650</t>
+          <t>400200651</t>
         </is>
       </c>
       <c r="C129" s="24" t="inlineStr">
         <is>
-          <t>60642</t>
+          <t>60643</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>Pneumatic nipple 10mm</t>
+          <t>Pneumatic nipple 12mm</t>
         </is>
       </c>
       <c r="E129" s="25" t="inlineStr">
@@ -31962,31 +31962,31 @@
         <v>6</v>
       </c>
       <c r="J129" s="26" t="n">
-        <v>42.1</v>
+        <v>57.89</v>
       </c>
       <c r="K129" s="26" t="n">
-        <v>252.6</v>
+        <v>347.34</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="21" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>272</t>
         </is>
       </c>
       <c r="B130" s="21" t="inlineStr">
         <is>
-          <t>400200651</t>
+          <t>400200656</t>
         </is>
       </c>
       <c r="C130" s="21" t="inlineStr">
         <is>
-          <t>60643</t>
+          <t>60648</t>
         </is>
       </c>
       <c r="D130" s="22" t="inlineStr">
         <is>
-          <t>Pneumatic nipple 12mm</t>
+          <t>Hose clamp 3/4 Inch</t>
         </is>
       </c>
       <c r="E130" s="22" t="inlineStr">
@@ -32000,40 +32000,40 @@
         </is>
       </c>
       <c r="G130" s="23" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="H130" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I130" s="23" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J130" s="23" t="n">
-        <v>57.89</v>
+        <v>16.84</v>
       </c>
       <c r="K130" s="23" t="n">
-        <v>347.34</v>
+        <v>404.16</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="24" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B131" s="24" t="inlineStr">
         <is>
-          <t>400200656</t>
+          <t>400200677</t>
         </is>
       </c>
       <c r="C131" s="24" t="inlineStr">
         <is>
-          <t>60648</t>
+          <t>60669</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>Hose clamp 3/4 Inch</t>
+          <t>Hexagonal nut-bolt with washer (Metric Size)</t>
         </is>
       </c>
       <c r="E131" s="25" t="inlineStr">
@@ -32047,40 +32047,40 @@
         </is>
       </c>
       <c r="G131" s="26" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="H131" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I131" s="26" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J131" s="26" t="n">
-        <v>16.84</v>
+        <v>80</v>
       </c>
       <c r="K131" s="26" t="n">
-        <v>404.16</v>
+        <v>640</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="21" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>275</t>
         </is>
       </c>
       <c r="B132" s="21" t="inlineStr">
         <is>
-          <t>400200677</t>
+          <t>400200678</t>
         </is>
       </c>
       <c r="C132" s="21" t="inlineStr">
         <is>
-          <t>60669</t>
+          <t>60670</t>
         </is>
       </c>
       <c r="D132" s="22" t="inlineStr">
         <is>
-          <t>Hexagonal nut-bolt with washer (Metric Size)</t>
+          <t>Hexagonal nut-bolt (Standard Size)</t>
         </is>
       </c>
       <c r="E132" s="22" t="inlineStr">
@@ -32094,40 +32094,40 @@
         </is>
       </c>
       <c r="G132" s="23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H132" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I132" s="23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J132" s="23" t="n">
-        <v>80</v>
+        <v>38.2272</v>
       </c>
       <c r="K132" s="23" t="n">
-        <v>640</v>
+        <v>267.59023844</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
       <c r="A133" s="24" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>280</t>
         </is>
       </c>
       <c r="B133" s="24" t="inlineStr">
         <is>
-          <t>400200678</t>
+          <t>400200692</t>
         </is>
       </c>
       <c r="C133" s="24" t="inlineStr">
         <is>
-          <t>60670</t>
+          <t>60684</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>Hexagonal nut-bolt (Standard Size)</t>
+          <t>Grease EP-000</t>
         </is>
       </c>
       <c r="E133" s="25" t="inlineStr">
@@ -32137,44 +32137,44 @@
       </c>
       <c r="F133" s="24" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G133" s="26" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="H133" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I133" s="26" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="J133" s="26" t="n">
-        <v>38.2272</v>
+        <v>694.9202</v>
       </c>
       <c r="K133" s="26" t="n">
-        <v>267.59023844</v>
+        <v>43779.9739545</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
       <c r="A134" s="21" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>284</t>
         </is>
       </c>
       <c r="B134" s="21" t="inlineStr">
         <is>
-          <t>400200692</t>
+          <t>400200713</t>
         </is>
       </c>
       <c r="C134" s="21" t="inlineStr">
         <is>
-          <t>60684</t>
+          <t>60705</t>
         </is>
       </c>
       <c r="D134" s="22" t="inlineStr">
         <is>
-          <t>Grease EP-000</t>
+          <t>Toggle pin</t>
         </is>
       </c>
       <c r="E134" s="22" t="inlineStr">
@@ -32184,44 +32184,44 @@
       </c>
       <c r="F134" s="21" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G134" s="23" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="H134" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I134" s="23" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="J134" s="23" t="n">
-        <v>694.9202</v>
+        <v>135.59</v>
       </c>
       <c r="K134" s="23" t="n">
-        <v>43779.9739545</v>
+        <v>135.59</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="24" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>287</t>
         </is>
       </c>
       <c r="B135" s="24" t="inlineStr">
         <is>
-          <t>400200713</t>
+          <t>400200743</t>
         </is>
       </c>
       <c r="C135" s="24" t="inlineStr">
         <is>
-          <t>60705</t>
+          <t>60735</t>
         </is>
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>Toggle pin</t>
+          <t>Thread union</t>
         </is>
       </c>
       <c r="E135" s="25" t="inlineStr">
@@ -32235,40 +32235,40 @@
         </is>
       </c>
       <c r="G135" s="26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H135" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I135" s="26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J135" s="26" t="n">
-        <v>135.59</v>
+        <v>678.1986000000001</v>
       </c>
       <c r="K135" s="26" t="n">
-        <v>135.59</v>
+        <v>4747.39000001</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
       <c r="A136" s="21" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>290</t>
         </is>
       </c>
       <c r="B136" s="21" t="inlineStr">
         <is>
-          <t>400200743</t>
+          <t>400200758</t>
         </is>
       </c>
       <c r="C136" s="21" t="inlineStr">
         <is>
-          <t>60735</t>
+          <t>60750</t>
         </is>
       </c>
       <c r="D136" s="22" t="inlineStr">
         <is>
-          <t>Thread union</t>
+          <t>G.I Elbow 1.5``</t>
         </is>
       </c>
       <c r="E136" s="22" t="inlineStr">
@@ -32282,40 +32282,40 @@
         </is>
       </c>
       <c r="G136" s="23" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H136" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I136" s="23" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J136" s="23" t="n">
-        <v>678.1986000000001</v>
+        <v>326.31</v>
       </c>
       <c r="K136" s="23" t="n">
-        <v>4747.39000001</v>
+        <v>4894.65</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="24" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>296</t>
         </is>
       </c>
       <c r="B137" s="24" t="inlineStr">
         <is>
-          <t>400200758</t>
+          <t>400200852</t>
         </is>
       </c>
       <c r="C137" s="24" t="inlineStr">
         <is>
-          <t>60750</t>
+          <t>60844</t>
         </is>
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>G.I Elbow 1.5``</t>
+          <t>MS Rod 8mm</t>
         </is>
       </c>
       <c r="E137" s="25" t="inlineStr">
@@ -32325,44 +32325,44 @@
       </c>
       <c r="F137" s="24" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G137" s="26" t="n">
-        <v>15</v>
+        <v>600</v>
       </c>
       <c r="H137" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I137" s="26" t="n">
-        <v>15</v>
+        <v>600</v>
       </c>
       <c r="J137" s="26" t="n">
-        <v>326.31</v>
+        <v>103.8595</v>
       </c>
       <c r="K137" s="26" t="n">
-        <v>4894.65</v>
+        <v>62315.7</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
       <c r="A138" s="21" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>297</t>
         </is>
       </c>
       <c r="B138" s="21" t="inlineStr">
         <is>
-          <t>400200851</t>
+          <t>400200871</t>
         </is>
       </c>
       <c r="C138" s="21" t="inlineStr">
         <is>
-          <t>60843</t>
+          <t>60863</t>
         </is>
       </c>
       <c r="D138" s="22" t="inlineStr">
         <is>
-          <t>MS Rod 10mm</t>
+          <t>Flap disk 4`` (Grade-220)</t>
         </is>
       </c>
       <c r="E138" s="22" t="inlineStr">
@@ -32372,44 +32372,44 @@
       </c>
       <c r="F138" s="21" t="inlineStr">
         <is>
-          <t>Feet</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G138" s="23" t="n">
-        <v>600</v>
+        <v>6</v>
       </c>
       <c r="H138" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I138" s="23" t="n">
-        <v>600</v>
+        <v>6</v>
       </c>
       <c r="J138" s="23" t="n">
-        <v>26.18</v>
+        <v>55.79</v>
       </c>
       <c r="K138" s="23" t="n">
-        <v>15708</v>
+        <v>334.74</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
       <c r="A139" s="24" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>302</t>
         </is>
       </c>
       <c r="B139" s="24" t="inlineStr">
         <is>
-          <t>400200852</t>
+          <t>400201021</t>
         </is>
       </c>
       <c r="C139" s="24" t="inlineStr">
         <is>
-          <t>60844</t>
+          <t>61013</t>
         </is>
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>MS Rod 8mm</t>
+          <t>Hand tap 3/16  (10 Pcs/set)</t>
         </is>
       </c>
       <c r="E139" s="25" t="inlineStr">
@@ -32419,44 +32419,44 @@
       </c>
       <c r="F139" s="24" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G139" s="26" t="n">
-        <v>600</v>
+        <v>7</v>
       </c>
       <c r="H139" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I139" s="26" t="n">
-        <v>600</v>
+        <v>7</v>
       </c>
       <c r="J139" s="26" t="n">
-        <v>103.8595</v>
+        <v>341.3529</v>
       </c>
       <c r="K139" s="26" t="n">
-        <v>62315.7</v>
+        <v>2389.46999998</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
       <c r="A140" s="21" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B140" s="21" t="inlineStr">
         <is>
-          <t>400200871</t>
+          <t>400201059</t>
         </is>
       </c>
       <c r="C140" s="21" t="inlineStr">
         <is>
-          <t>60863</t>
+          <t>61051</t>
         </is>
       </c>
       <c r="D140" s="22" t="inlineStr">
         <is>
-          <t>Flap disk 4`` (Grade-220)</t>
+          <t>Arc welding rod 3.2mm</t>
         </is>
       </c>
       <c r="E140" s="22" t="inlineStr">
@@ -32466,44 +32466,44 @@
       </c>
       <c r="F140" s="21" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>PKT</t>
         </is>
       </c>
       <c r="G140" s="23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H140" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I140" s="23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J140" s="23" t="n">
-        <v>55.79</v>
+        <v>1157.89</v>
       </c>
       <c r="K140" s="23" t="n">
-        <v>334.74</v>
+        <v>1157.89</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
       <c r="A141" s="24" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>317</t>
         </is>
       </c>
       <c r="B141" s="24" t="inlineStr">
         <is>
-          <t>400201021</t>
+          <t>400201097</t>
         </is>
       </c>
       <c r="C141" s="24" t="inlineStr">
         <is>
-          <t>61013</t>
+          <t>61089</t>
         </is>
       </c>
       <c r="D141" s="25" t="inlineStr">
         <is>
-          <t>Hand tap 3/16  (10 Pcs/set)</t>
+          <t>Cutting plier 6Inch</t>
         </is>
       </c>
       <c r="E141" s="25" t="inlineStr">
@@ -32517,40 +32517,40 @@
         </is>
       </c>
       <c r="G141" s="26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H141" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I141" s="26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J141" s="26" t="n">
-        <v>341.3529</v>
+        <v>247.735</v>
       </c>
       <c r="K141" s="26" t="n">
-        <v>2389.46999998</v>
+        <v>1981.87985632</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="21" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>323</t>
         </is>
       </c>
       <c r="B142" s="21" t="inlineStr">
         <is>
-          <t>400201059</t>
+          <t>400201107</t>
         </is>
       </c>
       <c r="C142" s="21" t="inlineStr">
         <is>
-          <t>61051</t>
+          <t>61099</t>
         </is>
       </c>
       <c r="D142" s="22" t="inlineStr">
         <is>
-          <t>Arc welding rod 3.2mm</t>
+          <t>Flat screw driver 10Inch</t>
         </is>
       </c>
       <c r="E142" s="22" t="inlineStr">
@@ -32560,44 +32560,44 @@
       </c>
       <c r="F142" s="21" t="inlineStr">
         <is>
-          <t>PKT</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G142" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H142" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I142" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J142" s="23" t="n">
-        <v>1157.89</v>
+        <v>515.79</v>
       </c>
       <c r="K142" s="23" t="n">
-        <v>1157.89</v>
+        <v>1547.37</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="24" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>325</t>
         </is>
       </c>
       <c r="B143" s="24" t="inlineStr">
         <is>
-          <t>400201097</t>
+          <t>400201110</t>
         </is>
       </c>
       <c r="C143" s="24" t="inlineStr">
         <is>
-          <t>61089</t>
+          <t>61102</t>
         </is>
       </c>
       <c r="D143" s="25" t="inlineStr">
         <is>
-          <t>Cutting plier 6Inch</t>
+          <t>Star screw driver 10Inch</t>
         </is>
       </c>
       <c r="E143" s="25" t="inlineStr">
@@ -32611,40 +32611,40 @@
         </is>
       </c>
       <c r="G143" s="26" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H143" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I143" s="26" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J143" s="26" t="n">
-        <v>247.735</v>
+        <v>515.79</v>
       </c>
       <c r="K143" s="26" t="n">
-        <v>2725.08480244</v>
+        <v>515.79</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
       <c r="A144" s="21" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>330</t>
         </is>
       </c>
       <c r="B144" s="21" t="inlineStr">
         <is>
-          <t>400201107</t>
+          <t>400201313</t>
         </is>
       </c>
       <c r="C144" s="21" t="inlineStr">
         <is>
-          <t>61099</t>
+          <t>61305</t>
         </is>
       </c>
       <c r="D144" s="22" t="inlineStr">
         <is>
-          <t>Flat screw driver 10Inch</t>
+          <t>Pneumatic filter</t>
         </is>
       </c>
       <c r="E144" s="22" t="inlineStr">
@@ -32658,40 +32658,40 @@
         </is>
       </c>
       <c r="G144" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H144" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I144" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J144" s="23" t="n">
-        <v>515.79</v>
+        <v>2136.84</v>
       </c>
       <c r="K144" s="23" t="n">
-        <v>1547.37</v>
+        <v>4273.68</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
       <c r="A145" s="24" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>332</t>
         </is>
       </c>
       <c r="B145" s="24" t="inlineStr">
         <is>
-          <t>400201110</t>
+          <t>400201319</t>
         </is>
       </c>
       <c r="C145" s="24" t="inlineStr">
         <is>
-          <t>61102</t>
+          <t>61311</t>
         </is>
       </c>
       <c r="D145" s="25" t="inlineStr">
         <is>
-          <t>Star screw driver 10Inch</t>
+          <t>V-Belt A-type (A27)</t>
         </is>
       </c>
       <c r="E145" s="25" t="inlineStr">
@@ -32714,31 +32714,31 @@
         <v>1</v>
       </c>
       <c r="J145" s="26" t="n">
-        <v>515.79</v>
+        <v>289.47</v>
       </c>
       <c r="K145" s="26" t="n">
-        <v>515.79</v>
+        <v>289.47</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
       <c r="A146" s="21" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>333</t>
         </is>
       </c>
       <c r="B146" s="21" t="inlineStr">
         <is>
-          <t>400201313</t>
+          <t>400201327</t>
         </is>
       </c>
       <c r="C146" s="21" t="inlineStr">
         <is>
-          <t>61305</t>
+          <t>61319</t>
         </is>
       </c>
       <c r="D146" s="22" t="inlineStr">
         <is>
-          <t>Pneumatic filter</t>
+          <t>V-Belt A-type (A37)</t>
         </is>
       </c>
       <c r="E146" s="22" t="inlineStr">
@@ -32752,40 +32752,40 @@
         </is>
       </c>
       <c r="G146" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H146" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I146" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J146" s="23" t="n">
-        <v>2136.84</v>
+        <v>205.26</v>
       </c>
       <c r="K146" s="23" t="n">
-        <v>4273.68</v>
+        <v>205.26</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
       <c r="A147" s="24" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>334</t>
         </is>
       </c>
       <c r="B147" s="24" t="inlineStr">
         <is>
-          <t>400201319</t>
+          <t>400201328</t>
         </is>
       </c>
       <c r="C147" s="24" t="inlineStr">
         <is>
-          <t>61311</t>
+          <t>61320</t>
         </is>
       </c>
       <c r="D147" s="25" t="inlineStr">
         <is>
-          <t>V-Belt A-type (A27)</t>
+          <t>V-Belt A-type (A38)</t>
         </is>
       </c>
       <c r="E147" s="25" t="inlineStr">
@@ -32808,31 +32808,31 @@
         <v>1</v>
       </c>
       <c r="J147" s="26" t="n">
-        <v>289.47</v>
+        <v>145.2625</v>
       </c>
       <c r="K147" s="26" t="n">
-        <v>289.47</v>
+        <v>145.2625</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
       <c r="A148" s="21" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>338</t>
         </is>
       </c>
       <c r="B148" s="21" t="inlineStr">
         <is>
-          <t>400201327</t>
+          <t>400201333</t>
         </is>
       </c>
       <c r="C148" s="21" t="inlineStr">
         <is>
-          <t>61319</t>
+          <t>61325</t>
         </is>
       </c>
       <c r="D148" s="22" t="inlineStr">
         <is>
-          <t>V-Belt A-type (A37)</t>
+          <t>V-Belt A-type (A43)</t>
         </is>
       </c>
       <c r="E148" s="22" t="inlineStr">
@@ -32855,31 +32855,31 @@
         <v>1</v>
       </c>
       <c r="J148" s="23" t="n">
-        <v>205.26</v>
+        <v>238.5967</v>
       </c>
       <c r="K148" s="23" t="n">
-        <v>205.26</v>
+        <v>238.59666667</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
       <c r="A149" s="24" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>339</t>
         </is>
       </c>
       <c r="B149" s="24" t="inlineStr">
         <is>
-          <t>400201328</t>
+          <t>400201334</t>
         </is>
       </c>
       <c r="C149" s="24" t="inlineStr">
         <is>
-          <t>61320</t>
+          <t>61326</t>
         </is>
       </c>
       <c r="D149" s="25" t="inlineStr">
         <is>
-          <t>V-Belt A-type (A38)</t>
+          <t>V-Belt A-type (A44)</t>
         </is>
       </c>
       <c r="E149" s="25" t="inlineStr">
@@ -32902,31 +32902,31 @@
         <v>1</v>
       </c>
       <c r="J149" s="26" t="n">
-        <v>145.2625</v>
+        <v>252.63</v>
       </c>
       <c r="K149" s="26" t="n">
-        <v>145.2625</v>
+        <v>252.63</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
       <c r="A150" s="21" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>341</t>
         </is>
       </c>
       <c r="B150" s="21" t="inlineStr">
         <is>
-          <t>400201333</t>
+          <t>400201339</t>
         </is>
       </c>
       <c r="C150" s="21" t="inlineStr">
         <is>
-          <t>61325</t>
+          <t>61331</t>
         </is>
       </c>
       <c r="D150" s="22" t="inlineStr">
         <is>
-          <t>V-Belt A-type (A43)</t>
+          <t>V-Belt A-type (A50)</t>
         </is>
       </c>
       <c r="E150" s="22" t="inlineStr">
@@ -32949,31 +32949,31 @@
         <v>1</v>
       </c>
       <c r="J150" s="23" t="n">
-        <v>238.5967</v>
+        <v>236.84</v>
       </c>
       <c r="K150" s="23" t="n">
-        <v>238.59666667</v>
+        <v>236.84</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
       <c r="A151" s="24" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>342</t>
         </is>
       </c>
       <c r="B151" s="24" t="inlineStr">
         <is>
-          <t>400201334</t>
+          <t>400201348</t>
         </is>
       </c>
       <c r="C151" s="24" t="inlineStr">
         <is>
-          <t>61326</t>
+          <t>61340</t>
         </is>
       </c>
       <c r="D151" s="25" t="inlineStr">
         <is>
-          <t>V-Belt A-type (A44)</t>
+          <t>V-Belt A-type (A59)</t>
         </is>
       </c>
       <c r="E151" s="25" t="inlineStr">
@@ -32987,40 +32987,40 @@
         </is>
       </c>
       <c r="G151" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H151" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I151" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J151" s="26" t="n">
-        <v>252.63</v>
+        <v>278.95</v>
       </c>
       <c r="K151" s="26" t="n">
-        <v>252.63</v>
+        <v>557.9</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
       <c r="A152" s="21" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>343</t>
         </is>
       </c>
       <c r="B152" s="21" t="inlineStr">
         <is>
-          <t>400201339</t>
+          <t>400201351</t>
         </is>
       </c>
       <c r="C152" s="21" t="inlineStr">
         <is>
-          <t>61331</t>
+          <t>61343</t>
         </is>
       </c>
       <c r="D152" s="22" t="inlineStr">
         <is>
-          <t>V-Belt A-type (A50)</t>
+          <t>V-Belt A-type (A62)</t>
         </is>
       </c>
       <c r="E152" s="22" t="inlineStr">
@@ -33034,40 +33034,40 @@
         </is>
       </c>
       <c r="G152" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H152" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I152" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J152" s="23" t="n">
-        <v>236.84</v>
+        <v>272.5269</v>
       </c>
       <c r="K152" s="23" t="n">
-        <v>236.84</v>
+        <v>545.0538</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
       <c r="A153" s="24" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>344</t>
         </is>
       </c>
       <c r="B153" s="24" t="inlineStr">
         <is>
-          <t>400201348</t>
+          <t>400201352</t>
         </is>
       </c>
       <c r="C153" s="24" t="inlineStr">
         <is>
-          <t>61340</t>
+          <t>61344</t>
         </is>
       </c>
       <c r="D153" s="25" t="inlineStr">
         <is>
-          <t>V-Belt A-type (A59)</t>
+          <t>V-Belt A-type (A63)</t>
         </is>
       </c>
       <c r="E153" s="25" t="inlineStr">
@@ -33090,31 +33090,31 @@
         <v>2</v>
       </c>
       <c r="J153" s="26" t="n">
-        <v>278.95</v>
+        <v>294.74</v>
       </c>
       <c r="K153" s="26" t="n">
-        <v>557.9</v>
+        <v>589.48</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
       <c r="A154" s="21" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>347</t>
         </is>
       </c>
       <c r="B154" s="21" t="inlineStr">
         <is>
-          <t>400201351</t>
+          <t>400201378</t>
         </is>
       </c>
       <c r="C154" s="21" t="inlineStr">
         <is>
-          <t>61343</t>
+          <t>61370</t>
         </is>
       </c>
       <c r="D154" s="22" t="inlineStr">
         <is>
-          <t>V-Belt A-type (A62)</t>
+          <t>V-Belt B-type (B51)</t>
         </is>
       </c>
       <c r="E154" s="22" t="inlineStr">
@@ -33128,40 +33128,40 @@
         </is>
       </c>
       <c r="G154" s="23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H154" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I154" s="23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J154" s="23" t="n">
-        <v>272.5269</v>
+        <v>210.5263</v>
       </c>
       <c r="K154" s="23" t="n">
-        <v>545.0538</v>
+        <v>1263.1578</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
       <c r="A155" s="24" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>353</t>
         </is>
       </c>
       <c r="B155" s="24" t="inlineStr">
         <is>
-          <t>400201352</t>
+          <t>400201492</t>
         </is>
       </c>
       <c r="C155" s="24" t="inlineStr">
         <is>
-          <t>61344</t>
+          <t>61482</t>
         </is>
       </c>
       <c r="D155" s="25" t="inlineStr">
         <is>
-          <t>V-Belt A-type (A63)</t>
+          <t>Industrial Star Air Bit (Small)</t>
         </is>
       </c>
       <c r="E155" s="25" t="inlineStr">
@@ -33175,40 +33175,40 @@
         </is>
       </c>
       <c r="G155" s="26" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H155" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I155" s="26" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J155" s="26" t="n">
-        <v>294.74</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="K155" s="26" t="n">
-        <v>589.48</v>
+        <v>1684.2</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
       <c r="A156" s="21" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>354</t>
         </is>
       </c>
       <c r="B156" s="21" t="inlineStr">
         <is>
-          <t>400201378</t>
+          <t>400201500</t>
         </is>
       </c>
       <c r="C156" s="21" t="inlineStr">
         <is>
-          <t>61370</t>
+          <t>61490</t>
         </is>
       </c>
       <c r="D156" s="22" t="inlineStr">
         <is>
-          <t>V-Belt B-type (B51)</t>
+          <t>Butane gas</t>
         </is>
       </c>
       <c r="E156" s="22" t="inlineStr">
@@ -33222,40 +33222,40 @@
         </is>
       </c>
       <c r="G156" s="23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H156" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I156" s="23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J156" s="23" t="n">
-        <v>210.5263</v>
+        <v>150</v>
       </c>
       <c r="K156" s="23" t="n">
-        <v>1263.1578</v>
+        <v>300</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
       <c r="A157" s="24" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>358</t>
         </is>
       </c>
       <c r="B157" s="24" t="inlineStr">
         <is>
-          <t>400201492</t>
+          <t>400201529</t>
         </is>
       </c>
       <c r="C157" s="24" t="inlineStr">
         <is>
-          <t>61482</t>
+          <t>61519</t>
         </is>
       </c>
       <c r="D157" s="25" t="inlineStr">
         <is>
-          <t>Industrial Star Air Bit (Small)</t>
+          <t>Pneumatic flow regulator</t>
         </is>
       </c>
       <c r="E157" s="25" t="inlineStr">
@@ -33269,40 +33269,40 @@
         </is>
       </c>
       <c r="G157" s="26" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H157" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I157" s="26" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J157" s="26" t="n">
-        <v>84.20999999999999</v>
+        <v>76.315</v>
       </c>
       <c r="K157" s="26" t="n">
-        <v>1684.2</v>
+        <v>305.26</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
       <c r="A158" s="21" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>359</t>
         </is>
       </c>
       <c r="B158" s="21" t="inlineStr">
         <is>
-          <t>400201500</t>
+          <t>400201530</t>
         </is>
       </c>
       <c r="C158" s="21" t="inlineStr">
         <is>
-          <t>61490</t>
+          <t>61520</t>
         </is>
       </c>
       <c r="D158" s="22" t="inlineStr">
         <is>
-          <t>Butane gas</t>
+          <t>Drill chuck (1-13)mm B16</t>
         </is>
       </c>
       <c r="E158" s="22" t="inlineStr">
@@ -33316,40 +33316,40 @@
         </is>
       </c>
       <c r="G158" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H158" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I158" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J158" s="23" t="n">
-        <v>150</v>
+        <v>442.1</v>
       </c>
       <c r="K158" s="23" t="n">
-        <v>300</v>
+        <v>1326.3</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
       <c r="A159" s="24" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>366</t>
         </is>
       </c>
       <c r="B159" s="24" t="inlineStr">
         <is>
-          <t>400201529</t>
+          <t>400201548</t>
         </is>
       </c>
       <c r="C159" s="24" t="inlineStr">
         <is>
-          <t>61519</t>
+          <t>61538</t>
         </is>
       </c>
       <c r="D159" s="25" t="inlineStr">
         <is>
-          <t>Pneumatic flow regulator</t>
+          <t>Flat Screw Driver</t>
         </is>
       </c>
       <c r="E159" s="25" t="inlineStr">
@@ -33363,40 +33363,40 @@
         </is>
       </c>
       <c r="G159" s="26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H159" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I159" s="26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J159" s="26" t="n">
-        <v>76.315</v>
+        <v>200</v>
       </c>
       <c r="K159" s="26" t="n">
-        <v>305.26</v>
+        <v>200</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
       <c r="A160" s="21" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>370</t>
         </is>
       </c>
       <c r="B160" s="21" t="inlineStr">
         <is>
-          <t>400201530</t>
+          <t>400201565</t>
         </is>
       </c>
       <c r="C160" s="21" t="inlineStr">
         <is>
-          <t>61520</t>
+          <t>61555</t>
         </is>
       </c>
       <c r="D160" s="22" t="inlineStr">
         <is>
-          <t>Drill chuck (1-13)mm B16</t>
+          <t>Gas Burner</t>
         </is>
       </c>
       <c r="E160" s="22" t="inlineStr">
@@ -33410,40 +33410,40 @@
         </is>
       </c>
       <c r="G160" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H160" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I160" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J160" s="23" t="n">
-        <v>442.1</v>
+        <v>300</v>
       </c>
       <c r="K160" s="23" t="n">
-        <v>1326.3</v>
+        <v>600</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
       <c r="A161" s="24" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>371</t>
         </is>
       </c>
       <c r="B161" s="24" t="inlineStr">
         <is>
-          <t>400201548</t>
+          <t>400201783</t>
         </is>
       </c>
       <c r="C161" s="24" t="inlineStr">
         <is>
-          <t>61538</t>
+          <t>61773</t>
         </is>
       </c>
       <c r="D161" s="25" t="inlineStr">
         <is>
-          <t>Flat Screw Driver</t>
+          <t>Mobil (Omera HD-50)</t>
         </is>
       </c>
       <c r="E161" s="25" t="inlineStr">
@@ -33453,44 +33453,44 @@
       </c>
       <c r="F161" s="24" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="G161" s="26" t="n">
-        <v>1</v>
+        <v>205</v>
       </c>
       <c r="H161" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I161" s="26" t="n">
-        <v>1</v>
+        <v>205</v>
       </c>
       <c r="J161" s="26" t="n">
-        <v>200</v>
+        <v>218.18</v>
       </c>
       <c r="K161" s="26" t="n">
-        <v>200</v>
+        <v>44726.9</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
       <c r="A162" s="21" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>372</t>
         </is>
       </c>
       <c r="B162" s="21" t="inlineStr">
         <is>
-          <t>400201565</t>
+          <t>400201784</t>
         </is>
       </c>
       <c r="C162" s="21" t="inlineStr">
         <is>
-          <t>61555</t>
+          <t>61774</t>
         </is>
       </c>
       <c r="D162" s="22" t="inlineStr">
         <is>
-          <t>Gas Burner</t>
+          <t>Vulcan Mobil</t>
         </is>
       </c>
       <c r="E162" s="22" t="inlineStr">
@@ -33500,44 +33500,44 @@
       </c>
       <c r="F162" s="21" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="G162" s="23" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="H162" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I162" s="23" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J162" s="23" t="n">
-        <v>300</v>
+        <v>465.1133</v>
       </c>
       <c r="K162" s="23" t="n">
-        <v>600</v>
+        <v>13953.3999999</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
       <c r="A163" s="24" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>384</t>
         </is>
       </c>
       <c r="B163" s="24" t="inlineStr">
         <is>
-          <t>400201783</t>
+          <t>400202117</t>
         </is>
       </c>
       <c r="C163" s="24" t="inlineStr">
         <is>
-          <t>61773</t>
+          <t>62107</t>
         </is>
       </c>
       <c r="D163" s="25" t="inlineStr">
         <is>
-          <t>Mobil (Omera HD-50)</t>
+          <t>Insulation tape</t>
         </is>
       </c>
       <c r="E163" s="25" t="inlineStr">
@@ -33547,44 +33547,44 @@
       </c>
       <c r="F163" s="24" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G163" s="26" t="n">
-        <v>205</v>
+        <v>5</v>
       </c>
       <c r="H163" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I163" s="26" t="n">
-        <v>205</v>
+        <v>5</v>
       </c>
       <c r="J163" s="26" t="n">
-        <v>218.18</v>
+        <v>21.05</v>
       </c>
       <c r="K163" s="26" t="n">
-        <v>44726.9</v>
+        <v>105.25</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
       <c r="A164" s="21" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>386</t>
         </is>
       </c>
       <c r="B164" s="21" t="inlineStr">
         <is>
-          <t>400201784</t>
+          <t>400202126</t>
         </is>
       </c>
       <c r="C164" s="21" t="inlineStr">
         <is>
-          <t>61774</t>
+          <t>62116</t>
         </is>
       </c>
       <c r="D164" s="22" t="inlineStr">
         <is>
-          <t>Vulcan Mobil</t>
+          <t>SS Allen bolt with Nut-Washer (8x50)mm</t>
         </is>
       </c>
       <c r="E164" s="22" t="inlineStr">
@@ -33594,44 +33594,44 @@
       </c>
       <c r="F164" s="21" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G164" s="23" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H164" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I164" s="23" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J164" s="23" t="n">
-        <v>465.1133</v>
+        <v>22.105</v>
       </c>
       <c r="K164" s="23" t="n">
-        <v>13953.3999999</v>
+        <v>530.52</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
       <c r="A165" s="24" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>389</t>
         </is>
       </c>
       <c r="B165" s="24" t="inlineStr">
         <is>
-          <t>400202117</t>
+          <t>400202160</t>
         </is>
       </c>
       <c r="C165" s="24" t="inlineStr">
         <is>
-          <t>62107</t>
+          <t>62150</t>
         </is>
       </c>
       <c r="D165" s="25" t="inlineStr">
         <is>
-          <t>Insulation tape</t>
+          <t>Crucible-500kg</t>
         </is>
       </c>
       <c r="E165" s="25" t="inlineStr">
@@ -33645,40 +33645,40 @@
         </is>
       </c>
       <c r="G165" s="26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H165" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I165" s="26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J165" s="26" t="n">
-        <v>21.05</v>
+        <v>172936.3381</v>
       </c>
       <c r="K165" s="26" t="n">
-        <v>147.35</v>
+        <v>691745.35246</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
       <c r="A166" s="21" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>390</t>
         </is>
       </c>
       <c r="B166" s="21" t="inlineStr">
         <is>
-          <t>400202126</t>
+          <t>400202161</t>
         </is>
       </c>
       <c r="C166" s="21" t="inlineStr">
         <is>
-          <t>62116</t>
+          <t>62151</t>
         </is>
       </c>
       <c r="D166" s="22" t="inlineStr">
         <is>
-          <t>SS Allen bolt with Nut-Washer (8x50)mm</t>
+          <t>Crucible-250kg</t>
         </is>
       </c>
       <c r="E166" s="22" t="inlineStr">
@@ -33692,40 +33692,40 @@
         </is>
       </c>
       <c r="G166" s="23" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="H166" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I166" s="23" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J166" s="23" t="n">
-        <v>22.105</v>
+        <v>122921.7341</v>
       </c>
       <c r="K166" s="23" t="n">
-        <v>530.52</v>
+        <v>491686.936408</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
       <c r="A167" s="24" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>391</t>
         </is>
       </c>
       <c r="B167" s="24" t="inlineStr">
         <is>
-          <t>400202160</t>
+          <t>400202162</t>
         </is>
       </c>
       <c r="C167" s="24" t="inlineStr">
         <is>
-          <t>62150</t>
+          <t>62152</t>
         </is>
       </c>
       <c r="D167" s="25" t="inlineStr">
         <is>
-          <t>Crucible-500kg</t>
+          <t>Furnace  Thermometer</t>
         </is>
       </c>
       <c r="E167" s="25" t="inlineStr">
@@ -33739,40 +33739,40 @@
         </is>
       </c>
       <c r="G167" s="26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H167" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I167" s="26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J167" s="26" t="n">
-        <v>172936.3381</v>
+        <v>7814.07</v>
       </c>
       <c r="K167" s="26" t="n">
-        <v>691745.35246</v>
+        <v>23442.21</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
       <c r="A168" s="21" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>392</t>
         </is>
       </c>
       <c r="B168" s="21" t="inlineStr">
         <is>
-          <t>400202161</t>
+          <t>400202163</t>
         </is>
       </c>
       <c r="C168" s="21" t="inlineStr">
         <is>
-          <t>62151</t>
+          <t>62153</t>
         </is>
       </c>
       <c r="D168" s="22" t="inlineStr">
         <is>
-          <t>Crucible-250kg</t>
+          <t>Automatic  Spray Header</t>
         </is>
       </c>
       <c r="E168" s="22" t="inlineStr">
@@ -33786,40 +33786,40 @@
         </is>
       </c>
       <c r="G168" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H168" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I168" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J168" s="23" t="n">
-        <v>122921.7341</v>
+        <v>53921.651</v>
       </c>
       <c r="K168" s="23" t="n">
-        <v>491686.936408</v>
+        <v>53921.651018</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
       <c r="A169" s="24" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>393</t>
         </is>
       </c>
       <c r="B169" s="24" t="inlineStr">
         <is>
-          <t>400202162</t>
+          <t>400202164</t>
         </is>
       </c>
       <c r="C169" s="24" t="inlineStr">
         <is>
-          <t>62152</t>
+          <t>62154</t>
         </is>
       </c>
       <c r="D169" s="25" t="inlineStr">
         <is>
-          <t>Furnace  Thermometer</t>
+          <t>Furnace Coil-500Kg</t>
         </is>
       </c>
       <c r="E169" s="25" t="inlineStr">
@@ -33833,40 +33833,40 @@
         </is>
       </c>
       <c r="G169" s="26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H169" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I169" s="26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J169" s="26" t="n">
-        <v>7814.07</v>
+        <v>51257.66</v>
       </c>
       <c r="K169" s="26" t="n">
-        <v>23442.21</v>
+        <v>512576.6</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
       <c r="A170" s="21" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>394</t>
         </is>
       </c>
       <c r="B170" s="21" t="inlineStr">
         <is>
-          <t>400202163</t>
+          <t>400202165</t>
         </is>
       </c>
       <c r="C170" s="21" t="inlineStr">
         <is>
-          <t>62153</t>
+          <t>62155</t>
         </is>
       </c>
       <c r="D170" s="22" t="inlineStr">
         <is>
-          <t>Automatic  Spray Header</t>
+          <t>Furnace Coil-250Kg</t>
         </is>
       </c>
       <c r="E170" s="22" t="inlineStr">
@@ -33880,40 +33880,40 @@
         </is>
       </c>
       <c r="G170" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H170" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I170" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J170" s="23" t="n">
-        <v>53921.651</v>
+        <v>37689.45</v>
       </c>
       <c r="K170" s="23" t="n">
-        <v>53921.651018</v>
+        <v>75378.89999999999</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
       <c r="A171" s="24" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>395</t>
         </is>
       </c>
       <c r="B171" s="24" t="inlineStr">
         <is>
-          <t>400202164</t>
+          <t>400202166</t>
         </is>
       </c>
       <c r="C171" s="24" t="inlineStr">
         <is>
-          <t>62154</t>
+          <t>62156</t>
         </is>
       </c>
       <c r="D171" s="25" t="inlineStr">
         <is>
-          <t>Furnace Coil-500Kg</t>
+          <t>Coil Connector</t>
         </is>
       </c>
       <c r="E171" s="25" t="inlineStr">
@@ -33927,40 +33927,40 @@
         </is>
       </c>
       <c r="G171" s="26" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H171" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I171" s="26" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="J171" s="26" t="n">
-        <v>51257.66</v>
+        <v>2261.37</v>
       </c>
       <c r="K171" s="26" t="n">
-        <v>512576.6</v>
+        <v>54272.88</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
       <c r="A172" s="21" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>396</t>
         </is>
       </c>
       <c r="B172" s="21" t="inlineStr">
         <is>
-          <t>400202165</t>
+          <t>400202167</t>
         </is>
       </c>
       <c r="C172" s="21" t="inlineStr">
         <is>
-          <t>62155</t>
+          <t>62157</t>
         </is>
       </c>
       <c r="D172" s="22" t="inlineStr">
         <is>
-          <t>Furnace Coil-250Kg</t>
+          <t>Mold Nut-Bolt / Tee/ Clamp</t>
         </is>
       </c>
       <c r="E172" s="22" t="inlineStr">
@@ -33974,40 +33974,40 @@
         </is>
       </c>
       <c r="G172" s="23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H172" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I172" s="23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J172" s="23" t="n">
-        <v>37689.45</v>
+        <v>53.3267</v>
       </c>
       <c r="K172" s="23" t="n">
-        <v>75378.89999999999</v>
+        <v>319.9602</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
       <c r="A173" s="24" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>397</t>
         </is>
       </c>
       <c r="B173" s="24" t="inlineStr">
         <is>
-          <t>400202166</t>
+          <t>400202168</t>
         </is>
       </c>
       <c r="C173" s="24" t="inlineStr">
         <is>
-          <t>62156</t>
+          <t>62158</t>
         </is>
       </c>
       <c r="D173" s="25" t="inlineStr">
         <is>
-          <t>Coil Connector</t>
+          <t>Nut -Bolt/ Tee</t>
         </is>
       </c>
       <c r="E173" s="25" t="inlineStr">
@@ -34021,40 +34021,40 @@
         </is>
       </c>
       <c r="G173" s="26" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H173" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I173" s="26" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J173" s="26" t="n">
-        <v>2261.37</v>
+        <v>30</v>
       </c>
       <c r="K173" s="26" t="n">
-        <v>54272.88</v>
+        <v>360</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
       <c r="A174" s="21" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>402</t>
         </is>
       </c>
       <c r="B174" s="21" t="inlineStr">
         <is>
-          <t>400202167</t>
+          <t>400202204</t>
         </is>
       </c>
       <c r="C174" s="21" t="inlineStr">
         <is>
-          <t>62157</t>
+          <t>62194</t>
         </is>
       </c>
       <c r="D174" s="22" t="inlineStr">
         <is>
-          <t>Mold Nut-Bolt / Tee/ Clamp</t>
+          <t>1``x1/2`` Tee socket</t>
         </is>
       </c>
       <c r="E174" s="22" t="inlineStr">
@@ -34068,40 +34068,40 @@
         </is>
       </c>
       <c r="G174" s="23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H174" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I174" s="23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J174" s="23" t="n">
-        <v>53.3267</v>
+        <v>108.42</v>
       </c>
       <c r="K174" s="23" t="n">
-        <v>319.9602</v>
+        <v>433.68</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
       <c r="A175" s="24" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>403</t>
         </is>
       </c>
       <c r="B175" s="24" t="inlineStr">
         <is>
-          <t>400202168</t>
+          <t>400202205</t>
         </is>
       </c>
       <c r="C175" s="24" t="inlineStr">
         <is>
-          <t>62158</t>
+          <t>62195</t>
         </is>
       </c>
       <c r="D175" s="25" t="inlineStr">
         <is>
-          <t>Nut -Bolt/ Tee</t>
+          <t>1`` Thread union</t>
         </is>
       </c>
       <c r="E175" s="25" t="inlineStr">
@@ -34115,40 +34115,40 @@
         </is>
       </c>
       <c r="G175" s="26" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H175" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I175" s="26" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J175" s="26" t="n">
-        <v>30</v>
+        <v>302.765</v>
       </c>
       <c r="K175" s="26" t="n">
-        <v>360</v>
+        <v>605.53</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
       <c r="A176" s="21" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>404</t>
         </is>
       </c>
       <c r="B176" s="21" t="inlineStr">
         <is>
-          <t>400202204</t>
+          <t>400202206</t>
         </is>
       </c>
       <c r="C176" s="21" t="inlineStr">
         <is>
-          <t>62194</t>
+          <t>62196</t>
         </is>
       </c>
       <c r="D176" s="22" t="inlineStr">
         <is>
-          <t>1``x1/2`` Tee socket</t>
+          <t>1`` MS thread elbow</t>
         </is>
       </c>
       <c r="E176" s="22" t="inlineStr">
@@ -34171,31 +34171,31 @@
         <v>4</v>
       </c>
       <c r="J176" s="23" t="n">
-        <v>108.42</v>
+        <v>131.84</v>
       </c>
       <c r="K176" s="23" t="n">
-        <v>433.68</v>
+        <v>527.36</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
       <c r="A177" s="24" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>408</t>
         </is>
       </c>
       <c r="B177" s="24" t="inlineStr">
         <is>
-          <t>400202205</t>
+          <t>400202318</t>
         </is>
       </c>
       <c r="C177" s="24" t="inlineStr">
         <is>
-          <t>62195</t>
+          <t>62308</t>
         </is>
       </c>
       <c r="D177" s="25" t="inlineStr">
         <is>
-          <t>1`` Thread union</t>
+          <t>Pneumatic tee socket 8mm</t>
         </is>
       </c>
       <c r="E177" s="25" t="inlineStr">
@@ -34209,40 +34209,40 @@
         </is>
       </c>
       <c r="G177" s="26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H177" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I177" s="26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J177" s="26" t="n">
-        <v>302.765</v>
+        <v>34.205</v>
       </c>
       <c r="K177" s="26" t="n">
-        <v>605.53</v>
+        <v>205.23</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
       <c r="A178" s="21" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>410</t>
         </is>
       </c>
       <c r="B178" s="21" t="inlineStr">
         <is>
-          <t>400202206</t>
+          <t>400202323</t>
         </is>
       </c>
       <c r="C178" s="21" t="inlineStr">
         <is>
-          <t>62196</t>
+          <t>62313</t>
         </is>
       </c>
       <c r="D178" s="22" t="inlineStr">
         <is>
-          <t>1`` MS thread elbow</t>
+          <t>Pneumatic pipe 4mm</t>
         </is>
       </c>
       <c r="E178" s="22" t="inlineStr">
@@ -34252,44 +34252,44 @@
       </c>
       <c r="F178" s="21" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Feet</t>
         </is>
       </c>
       <c r="G178" s="23" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="H178" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I178" s="23" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="J178" s="23" t="n">
-        <v>131.84</v>
+        <v>7.37</v>
       </c>
       <c r="K178" s="23" t="n">
-        <v>527.36</v>
+        <v>368.5</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
       <c r="A179" s="24" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>411</t>
         </is>
       </c>
       <c r="B179" s="24" t="inlineStr">
         <is>
-          <t>400202318</t>
+          <t>400202327</t>
         </is>
       </c>
       <c r="C179" s="24" t="inlineStr">
         <is>
-          <t>62308</t>
+          <t>62317</t>
         </is>
       </c>
       <c r="D179" s="25" t="inlineStr">
         <is>
-          <t>Pneumatic tee socket 8mm</t>
+          <t>Nicorn Wire</t>
         </is>
       </c>
       <c r="E179" s="25" t="inlineStr">
@@ -34299,44 +34299,44 @@
       </c>
       <c r="F179" s="24" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G179" s="26" t="n">
-        <v>6</v>
+        <v>14.8</v>
       </c>
       <c r="H179" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I179" s="26" t="n">
-        <v>6</v>
+        <v>14.8</v>
       </c>
       <c r="J179" s="26" t="n">
-        <v>34.205</v>
+        <v>526.3157</v>
       </c>
       <c r="K179" s="26" t="n">
-        <v>205.23</v>
+        <v>7789.47236</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
       <c r="A180" s="21" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>422</t>
         </is>
       </c>
       <c r="B180" s="21" t="inlineStr">
         <is>
-          <t>400202323</t>
+          <t>400202380</t>
         </is>
       </c>
       <c r="C180" s="21" t="inlineStr">
         <is>
-          <t>62313</t>
+          <t>62370</t>
         </is>
       </c>
       <c r="D180" s="22" t="inlineStr">
         <is>
-          <t>Pneumatic pipe 4mm</t>
+          <t>MS BAND 3/4``</t>
         </is>
       </c>
       <c r="E180" s="22" t="inlineStr">
@@ -34346,44 +34346,44 @@
       </c>
       <c r="F180" s="21" t="inlineStr">
         <is>
-          <t>Feet</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G180" s="23" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="H180" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I180" s="23" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="J180" s="23" t="n">
-        <v>7.37</v>
+        <v>630.4111</v>
       </c>
       <c r="K180" s="23" t="n">
-        <v>368.5</v>
+        <v>11347.39999998</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
       <c r="A181" s="24" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>437</t>
         </is>
       </c>
       <c r="B181" s="24" t="inlineStr">
         <is>
-          <t>400202327</t>
+          <t>400202555</t>
         </is>
       </c>
       <c r="C181" s="24" t="inlineStr">
         <is>
-          <t>62317</t>
+          <t>62545</t>
         </is>
       </c>
       <c r="D181" s="25" t="inlineStr">
         <is>
-          <t>Nicorn Wire</t>
+          <t>Oil Suction Filter (Silver) (174mm×78mm)</t>
         </is>
       </c>
       <c r="E181" s="25" t="inlineStr">
@@ -34393,44 +34393,44 @@
       </c>
       <c r="F181" s="24" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G181" s="26" t="n">
-        <v>14.8</v>
+        <v>2</v>
       </c>
       <c r="H181" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I181" s="26" t="n">
-        <v>14.8</v>
+        <v>2</v>
       </c>
       <c r="J181" s="26" t="n">
-        <v>526.3157</v>
+        <v>101.5038</v>
       </c>
       <c r="K181" s="26" t="n">
-        <v>7789.47236</v>
+        <v>203.0075188</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
       <c r="A182" s="21" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>438</t>
         </is>
       </c>
       <c r="B182" s="21" t="inlineStr">
         <is>
-          <t>400202380</t>
+          <t>400202567</t>
         </is>
       </c>
       <c r="C182" s="21" t="inlineStr">
         <is>
-          <t>62370</t>
+          <t>62557</t>
         </is>
       </c>
       <c r="D182" s="22" t="inlineStr">
         <is>
-          <t>MS BAND 3/4``</t>
+          <t>Robot sensor</t>
         </is>
       </c>
       <c r="E182" s="22" t="inlineStr">
@@ -34444,40 +34444,40 @@
         </is>
       </c>
       <c r="G182" s="23" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H182" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I182" s="23" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J182" s="23" t="n">
-        <v>630.4111</v>
+        <v>789.42</v>
       </c>
       <c r="K182" s="23" t="n">
-        <v>11347.39999998</v>
+        <v>1578.84</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
       <c r="A183" s="24" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>447</t>
         </is>
       </c>
       <c r="B183" s="24" t="inlineStr">
         <is>
-          <t>400202555</t>
+          <t>400202677</t>
         </is>
       </c>
       <c r="C183" s="24" t="inlineStr">
         <is>
-          <t>62545</t>
+          <t>62667</t>
         </is>
       </c>
       <c r="D183" s="25" t="inlineStr">
         <is>
-          <t>Oil Suction Filter (Silver) (174mm×78mm)</t>
+          <t>G.I Nipple 1.5 Inch</t>
         </is>
       </c>
       <c r="E183" s="25" t="inlineStr">
@@ -34491,40 +34491,40 @@
         </is>
       </c>
       <c r="G183" s="26" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H183" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I183" s="26" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J183" s="26" t="n">
-        <v>101.5038</v>
+        <v>248.6838</v>
       </c>
       <c r="K183" s="26" t="n">
-        <v>203.0075188</v>
+        <v>3978.94</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
       <c r="A184" s="21" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>449</t>
         </is>
       </c>
       <c r="B184" s="21" t="inlineStr">
         <is>
-          <t>400202567</t>
+          <t>400202718</t>
         </is>
       </c>
       <c r="C184" s="21" t="inlineStr">
         <is>
-          <t>62557</t>
+          <t>62708</t>
         </is>
       </c>
       <c r="D184" s="22" t="inlineStr">
         <is>
-          <t>Robot sensor</t>
+          <t>Scissors</t>
         </is>
       </c>
       <c r="E184" s="22" t="inlineStr">
@@ -34538,40 +34538,40 @@
         </is>
       </c>
       <c r="G184" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H184" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I184" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J184" s="23" t="n">
-        <v>789.42</v>
+        <v>153.5067</v>
       </c>
       <c r="K184" s="23" t="n">
-        <v>1578.84</v>
+        <v>153.50666667</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
       <c r="A185" s="24" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>466</t>
         </is>
       </c>
       <c r="B185" s="24" t="inlineStr">
         <is>
-          <t>400202677</t>
+          <t>400202811</t>
         </is>
       </c>
       <c r="C185" s="24" t="inlineStr">
         <is>
-          <t>62667</t>
+          <t>62801</t>
         </is>
       </c>
       <c r="D185" s="25" t="inlineStr">
         <is>
-          <t>G.I Nipple 1.5 Inch</t>
+          <t>1/2inch g.i socket</t>
         </is>
       </c>
       <c r="E185" s="25" t="inlineStr">
@@ -34585,40 +34585,40 @@
         </is>
       </c>
       <c r="G185" s="26" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H185" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I185" s="26" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J185" s="26" t="n">
-        <v>248.6838</v>
+        <v>324.208</v>
       </c>
       <c r="K185" s="26" t="n">
-        <v>3978.94</v>
+        <v>8105.2</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
       <c r="A186" s="21" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>469</t>
         </is>
       </c>
       <c r="B186" s="21" t="inlineStr">
         <is>
-          <t>400202718</t>
+          <t>400202843</t>
         </is>
       </c>
       <c r="C186" s="21" t="inlineStr">
         <is>
-          <t>62708</t>
+          <t>62833</t>
         </is>
       </c>
       <c r="D186" s="22" t="inlineStr">
         <is>
-          <t>Scissors</t>
+          <t>Thyristor power regulating trigger AIJK6 three-phase phase shift/cycle zero crossing</t>
         </is>
       </c>
       <c r="E186" s="22" t="inlineStr">
@@ -34632,40 +34632,40 @@
         </is>
       </c>
       <c r="G186" s="23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H186" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I186" s="23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J186" s="23" t="n">
-        <v>153.5067</v>
+        <v>28270.7545</v>
       </c>
       <c r="K186" s="23" t="n">
-        <v>153.50666667</v>
+        <v>169624.526964</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
       <c r="A187" s="24" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>475</t>
         </is>
       </c>
       <c r="B187" s="24" t="inlineStr">
         <is>
-          <t>400202811</t>
+          <t>400202898</t>
         </is>
       </c>
       <c r="C187" s="24" t="inlineStr">
         <is>
-          <t>62801</t>
+          <t>62888</t>
         </is>
       </c>
       <c r="D187" s="25" t="inlineStr">
         <is>
-          <t>1/2inch g.i socket</t>
+          <t>Round Saw Blade 2.4``</t>
         </is>
       </c>
       <c r="E187" s="25" t="inlineStr">
@@ -34679,40 +34679,40 @@
         </is>
       </c>
       <c r="G187" s="26" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H187" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I187" s="26" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="J187" s="26" t="n">
-        <v>324.208</v>
+        <v>4933.3565</v>
       </c>
       <c r="K187" s="26" t="n">
-        <v>8105.2</v>
+        <v>197334.2608696</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
       <c r="A188" s="21" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>479</t>
         </is>
       </c>
       <c r="B188" s="21" t="inlineStr">
         <is>
-          <t>400202843</t>
+          <t>400202971</t>
         </is>
       </c>
       <c r="C188" s="21" t="inlineStr">
         <is>
-          <t>62833</t>
+          <t>62961</t>
         </is>
       </c>
       <c r="D188" s="22" t="inlineStr">
         <is>
-          <t>Thyristor power regulating trigger AIJK6 three-phase phase shift/cycle zero crossing</t>
+          <t>pneumatic Nipple (8mmPx10mmT)</t>
         </is>
       </c>
       <c r="E188" s="22" t="inlineStr">
@@ -34735,31 +34735,31 @@
         <v>6</v>
       </c>
       <c r="J188" s="23" t="n">
-        <v>28270.7545</v>
+        <v>57.89</v>
       </c>
       <c r="K188" s="23" t="n">
-        <v>169624.526964</v>
+        <v>347.34</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
       <c r="A189" s="24" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>480</t>
         </is>
       </c>
       <c r="B189" s="24" t="inlineStr">
         <is>
-          <t>400202898</t>
+          <t>400202976</t>
         </is>
       </c>
       <c r="C189" s="24" t="inlineStr">
         <is>
-          <t>62888</t>
+          <t>62966</t>
         </is>
       </c>
       <c r="D189" s="25" t="inlineStr">
         <is>
-          <t>Round Saw Blade 2.4``</t>
+          <t>Gate valve 1/2inch</t>
         </is>
       </c>
       <c r="E189" s="25" t="inlineStr">
@@ -34773,40 +34773,40 @@
         </is>
       </c>
       <c r="G189" s="26" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="H189" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I189" s="26" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="J189" s="26" t="n">
-        <v>4933.3565</v>
+        <v>463.1579</v>
       </c>
       <c r="K189" s="26" t="n">
-        <v>197334.2608696</v>
+        <v>1389.47358</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
       <c r="A190" s="21" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>486</t>
         </is>
       </c>
       <c r="B190" s="21" t="inlineStr">
         <is>
-          <t>400202971</t>
+          <t>400203008</t>
         </is>
       </c>
       <c r="C190" s="21" t="inlineStr">
         <is>
-          <t>62961</t>
+          <t>62998</t>
         </is>
       </c>
       <c r="D190" s="22" t="inlineStr">
         <is>
-          <t>pneumatic Nipple (8mmPx10mmT)</t>
+          <t>Trolley Wheel-6``</t>
         </is>
       </c>
       <c r="E190" s="22" t="inlineStr">
@@ -34820,40 +34820,40 @@
         </is>
       </c>
       <c r="G190" s="23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H190" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I190" s="23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J190" s="23" t="n">
-        <v>57.89</v>
+        <v>1552.6315</v>
       </c>
       <c r="K190" s="23" t="n">
-        <v>347.34</v>
+        <v>6210.52613336</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
       <c r="A191" s="24" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>493</t>
         </is>
       </c>
       <c r="B191" s="24" t="inlineStr">
         <is>
-          <t>400202976</t>
+          <t>400203037</t>
         </is>
       </c>
       <c r="C191" s="24" t="inlineStr">
         <is>
-          <t>62966</t>
+          <t>63027</t>
         </is>
       </c>
       <c r="D191" s="25" t="inlineStr">
         <is>
-          <t>Gate valve 1/2inch</t>
+          <t>Pneumatic Elbow (10mmx1/4inch)BSPT</t>
         </is>
       </c>
       <c r="E191" s="25" t="inlineStr">
@@ -34867,40 +34867,40 @@
         </is>
       </c>
       <c r="G191" s="26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H191" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I191" s="26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J191" s="26" t="n">
-        <v>463.1579</v>
+        <v>589.47</v>
       </c>
       <c r="K191" s="26" t="n">
-        <v>1389.47358</v>
+        <v>2357.88</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
       <c r="A192" s="21" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>498</t>
         </is>
       </c>
       <c r="B192" s="21" t="inlineStr">
         <is>
-          <t>400203008</t>
+          <t>400203085</t>
         </is>
       </c>
       <c r="C192" s="21" t="inlineStr">
         <is>
-          <t>62998</t>
+          <t>63075</t>
         </is>
       </c>
       <c r="D192" s="22" t="inlineStr">
         <is>
-          <t>Trolley Wheel-6``</t>
+          <t>GI 3/4 Gad nipple</t>
         </is>
       </c>
       <c r="E192" s="22" t="inlineStr">
@@ -34914,40 +34914,40 @@
         </is>
       </c>
       <c r="G192" s="23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H192" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I192" s="23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J192" s="23" t="n">
-        <v>1552.6315</v>
+        <v>59.475</v>
       </c>
       <c r="K192" s="23" t="n">
-        <v>6210.52613336</v>
+        <v>475.8</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
       <c r="A193" s="24" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B193" s="24" t="inlineStr">
         <is>
-          <t>400203037</t>
+          <t>400203090</t>
         </is>
       </c>
       <c r="C193" s="24" t="inlineStr">
         <is>
-          <t>63027</t>
+          <t>63080</t>
         </is>
       </c>
       <c r="D193" s="25" t="inlineStr">
         <is>
-          <t>Pneumatic Elbow (10mmx1/4inch)BSPT</t>
+          <t>Weight Scale Charger</t>
         </is>
       </c>
       <c r="E193" s="25" t="inlineStr">
@@ -34961,40 +34961,40 @@
         </is>
       </c>
       <c r="G193" s="26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H193" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I193" s="26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J193" s="26" t="n">
-        <v>589.47</v>
+        <v>263.15</v>
       </c>
       <c r="K193" s="26" t="n">
-        <v>2357.88</v>
+        <v>789.45</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
       <c r="A194" s="21" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>506</t>
         </is>
       </c>
       <c r="B194" s="21" t="inlineStr">
         <is>
-          <t>400203085</t>
+          <t>400203102</t>
         </is>
       </c>
       <c r="C194" s="21" t="inlineStr">
         <is>
-          <t>63075</t>
+          <t>63092</t>
         </is>
       </c>
       <c r="D194" s="22" t="inlineStr">
         <is>
-          <t>GI 3/4 Gad nipple</t>
+          <t>Steel wire</t>
         </is>
       </c>
       <c r="E194" s="22" t="inlineStr">
@@ -35004,44 +35004,44 @@
       </c>
       <c r="F194" s="21" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Mtr</t>
         </is>
       </c>
       <c r="G194" s="23" t="n">
-        <v>8</v>
+        <v>31.72</v>
       </c>
       <c r="H194" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I194" s="23" t="n">
-        <v>8</v>
+        <v>31.72</v>
       </c>
       <c r="J194" s="23" t="n">
-        <v>59.475</v>
+        <v>640.3262</v>
       </c>
       <c r="K194" s="23" t="n">
-        <v>475.8</v>
+        <v>20311.145600122</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
       <c r="A195" s="24" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>508</t>
         </is>
       </c>
       <c r="B195" s="24" t="inlineStr">
         <is>
-          <t>400203090</t>
+          <t>400203109</t>
         </is>
       </c>
       <c r="C195" s="24" t="inlineStr">
         <is>
-          <t>63080</t>
+          <t>63099</t>
         </is>
       </c>
       <c r="D195" s="25" t="inlineStr">
         <is>
-          <t>Weight Scale Charger</t>
+          <t>Brush 3 Inch</t>
         </is>
       </c>
       <c r="E195" s="25" t="inlineStr">
@@ -35055,40 +35055,40 @@
         </is>
       </c>
       <c r="G195" s="26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H195" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I195" s="26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J195" s="26" t="n">
-        <v>263.15</v>
+        <v>131.5767</v>
       </c>
       <c r="K195" s="26" t="n">
-        <v>789.45</v>
+        <v>263.15333334</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
       <c r="A196" s="21" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>510</t>
         </is>
       </c>
       <c r="B196" s="21" t="inlineStr">
         <is>
-          <t>400203102</t>
+          <t>400203173</t>
         </is>
       </c>
       <c r="C196" s="21" t="inlineStr">
         <is>
-          <t>63092</t>
+          <t>63164</t>
         </is>
       </c>
       <c r="D196" s="22" t="inlineStr">
         <is>
-          <t>Steel wire</t>
+          <t>MS Bolt</t>
         </is>
       </c>
       <c r="E196" s="22" t="inlineStr">
@@ -35098,44 +35098,44 @@
       </c>
       <c r="F196" s="21" t="inlineStr">
         <is>
-          <t>Mtr</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G196" s="23" t="n">
-        <v>31.72</v>
+        <v>12</v>
       </c>
       <c r="H196" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I196" s="23" t="n">
-        <v>31.72</v>
+        <v>12</v>
       </c>
       <c r="J196" s="23" t="n">
-        <v>640.3262</v>
+        <v>115.79</v>
       </c>
       <c r="K196" s="23" t="n">
-        <v>20311.145600122</v>
+        <v>1389.48</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
       <c r="A197" s="24" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>516</t>
         </is>
       </c>
       <c r="B197" s="24" t="inlineStr">
         <is>
-          <t>400203109</t>
+          <t>400203230</t>
         </is>
       </c>
       <c r="C197" s="24" t="inlineStr">
         <is>
-          <t>63099</t>
+          <t>63221</t>
         </is>
       </c>
       <c r="D197" s="25" t="inlineStr">
         <is>
-          <t>Brush 3 Inch</t>
+          <t>Galvanized MS Sheet-23</t>
         </is>
       </c>
       <c r="E197" s="25" t="inlineStr">
@@ -35145,44 +35145,44 @@
       </c>
       <c r="F197" s="24" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G197" s="26" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="H197" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I197" s="26" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="J197" s="26" t="n">
-        <v>131.5767</v>
+        <v>1270.0947</v>
       </c>
       <c r="K197" s="26" t="n">
-        <v>263.15333334</v>
+        <v>254018.94</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
       <c r="A198" s="21" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>521</t>
         </is>
       </c>
       <c r="B198" s="21" t="inlineStr">
         <is>
-          <t>400203173</t>
+          <t>400203318</t>
         </is>
       </c>
       <c r="C198" s="21" t="inlineStr">
         <is>
-          <t>63164</t>
+          <t>63308</t>
         </is>
       </c>
       <c r="D198" s="22" t="inlineStr">
         <is>
-          <t>MS Bolt</t>
+          <t>Ladle Cup 1.5kg</t>
         </is>
       </c>
       <c r="E198" s="22" t="inlineStr">
@@ -35196,40 +35196,40 @@
         </is>
       </c>
       <c r="G198" s="23" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H198" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I198" s="23" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J198" s="23" t="n">
-        <v>115.79</v>
+        <v>3110.8278</v>
       </c>
       <c r="K198" s="23" t="n">
-        <v>1389.48</v>
+        <v>12443.311304</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
       <c r="A199" s="24" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>522</t>
         </is>
       </c>
       <c r="B199" s="24" t="inlineStr">
         <is>
-          <t>400203230</t>
+          <t>400203319</t>
         </is>
       </c>
       <c r="C199" s="24" t="inlineStr">
         <is>
-          <t>63221</t>
+          <t>63309</t>
         </is>
       </c>
       <c r="D199" s="25" t="inlineStr">
         <is>
-          <t>Galvanized MS Sheet-23</t>
+          <t>Coil Connector Shaft L= 381 mm, D=14mm</t>
         </is>
       </c>
       <c r="E199" s="25" t="inlineStr">
@@ -35239,44 +35239,44 @@
       </c>
       <c r="F199" s="24" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G199" s="26" t="n">
-        <v>200</v>
+        <v>24</v>
       </c>
       <c r="H199" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I199" s="26" t="n">
-        <v>200</v>
+        <v>24</v>
       </c>
       <c r="J199" s="26" t="n">
-        <v>1270.0947</v>
+        <v>1991.0279</v>
       </c>
       <c r="K199" s="26" t="n">
-        <v>254018.94</v>
+        <v>47784.669576</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
       <c r="A200" s="21" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>523</t>
         </is>
       </c>
       <c r="B200" s="21" t="inlineStr">
         <is>
-          <t>400203318</t>
+          <t>400203320</t>
         </is>
       </c>
       <c r="C200" s="21" t="inlineStr">
         <is>
-          <t>63308</t>
+          <t>63310</t>
         </is>
       </c>
       <c r="D200" s="22" t="inlineStr">
         <is>
-          <t>Ladle Cup 1.5kg</t>
+          <t>Plunger Shot Sleeve</t>
         </is>
       </c>
       <c r="E200" s="22" t="inlineStr">
@@ -35290,40 +35290,40 @@
         </is>
       </c>
       <c r="G200" s="23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H200" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I200" s="23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J200" s="23" t="n">
-        <v>3110.8278</v>
+        <v>69993.7061</v>
       </c>
       <c r="K200" s="23" t="n">
-        <v>18664.966956</v>
+        <v>139987.412182</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
       <c r="A201" s="24" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>529</t>
         </is>
       </c>
       <c r="B201" s="24" t="inlineStr">
         <is>
-          <t>400203319</t>
+          <t>400203327</t>
         </is>
       </c>
       <c r="C201" s="24" t="inlineStr">
         <is>
-          <t>63309</t>
+          <t>63317</t>
         </is>
       </c>
       <c r="D201" s="25" t="inlineStr">
         <is>
-          <t>Coil Connector Shaft L= 381 mm, D=14mm</t>
+          <t>Handheld Magnetic Press Feeder-(Length-300mm).</t>
         </is>
       </c>
       <c r="E201" s="25" t="inlineStr">
@@ -35337,185 +35337,44 @@
         </is>
       </c>
       <c r="G201" s="26" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H201" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I201" s="26" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="J201" s="26" t="n">
-        <v>1991.0279</v>
+        <v>166.38</v>
       </c>
       <c r="K201" s="26" t="n">
-        <v>47784.669576</v>
-      </c>
-    </row>
-    <row r="202" ht="20" customHeight="1">
-      <c r="A202" s="21" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
-      <c r="B202" s="21" t="inlineStr">
-        <is>
-          <t>400203320</t>
-        </is>
-      </c>
-      <c r="C202" s="21" t="inlineStr">
-        <is>
-          <t>63310</t>
-        </is>
-      </c>
-      <c r="D202" s="22" t="inlineStr">
-        <is>
-          <t>Plunger Shot Sleeve</t>
-        </is>
-      </c>
-      <c r="E202" s="22" t="inlineStr">
-        <is>
-          <t>Mechanical Parts</t>
-        </is>
-      </c>
-      <c r="F202" s="21" t="inlineStr">
-        <is>
-          <t>Pcs</t>
-        </is>
-      </c>
-      <c r="G202" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="H202" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I202" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="J202" s="23" t="n">
-        <v>69993.7061</v>
-      </c>
-      <c r="K202" s="23" t="n">
-        <v>279974.824364</v>
-      </c>
-    </row>
-    <row r="203" ht="20" customHeight="1">
-      <c r="A203" s="24" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="B203" s="24" t="inlineStr">
-        <is>
-          <t>400203323</t>
-        </is>
-      </c>
-      <c r="C203" s="24" t="inlineStr">
-        <is>
-          <t>63313</t>
-        </is>
-      </c>
-      <c r="D203" s="25" t="inlineStr">
-        <is>
-          <t>Trolley Wheel-7`` OD×W:(7×2) Inch</t>
-        </is>
-      </c>
-      <c r="E203" s="25" t="inlineStr">
-        <is>
-          <t>Mechanical Parts</t>
-        </is>
-      </c>
-      <c r="F203" s="24" t="inlineStr">
-        <is>
-          <t>Set</t>
-        </is>
-      </c>
-      <c r="G203" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="H203" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I203" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="J203" s="26" t="n">
-        <v>1824.5617</v>
-      </c>
-      <c r="K203" s="26" t="n">
-        <v>3649.12346666</v>
-      </c>
-    </row>
-    <row r="204" ht="20" customHeight="1">
-      <c r="A204" s="21" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="B204" s="21" t="inlineStr">
-        <is>
-          <t>400203327</t>
-        </is>
-      </c>
-      <c r="C204" s="21" t="inlineStr">
-        <is>
-          <t>63317</t>
-        </is>
-      </c>
-      <c r="D204" s="22" t="inlineStr">
-        <is>
-          <t>Handheld Magnetic Press Feeder-(Length-300mm).</t>
-        </is>
-      </c>
-      <c r="E204" s="22" t="inlineStr">
-        <is>
-          <t>Mechanical Parts</t>
-        </is>
-      </c>
-      <c r="F204" s="21" t="inlineStr">
-        <is>
-          <t>Pcs</t>
-        </is>
-      </c>
-      <c r="G204" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="H204" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I204" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="J204" s="23" t="n">
-        <v>166.38</v>
-      </c>
-      <c r="K204" s="23" t="n">
         <v>1830.18</v>
       </c>
     </row>
-    <row r="205" ht="24" customHeight="1">
-      <c r="A205" s="27" t="inlineStr">
+    <row r="202" ht="24" customHeight="1">
+      <c r="A202" s="27" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B205" s="27" t="n"/>
-      <c r="C205" s="27" t="n"/>
-      <c r="D205" s="27" t="inlineStr">
-        <is>
-          <t>201 Items</t>
-        </is>
-      </c>
-      <c r="E205" s="27" t="n"/>
-      <c r="F205" s="27" t="n"/>
-      <c r="G205" s="27" t="n"/>
-      <c r="H205" s="27" t="n"/>
-      <c r="I205" s="28" t="n">
-        <v>4385.05</v>
-      </c>
-      <c r="J205" s="27" t="n"/>
-      <c r="K205" s="28" t="n">
-        <v>4588920.910186038</v>
+      <c r="B202" s="27" t="n"/>
+      <c r="C202" s="27" t="n"/>
+      <c r="D202" s="27" t="inlineStr">
+        <is>
+          <t>198 Items</t>
+        </is>
+      </c>
+      <c r="E202" s="27" t="n"/>
+      <c r="F202" s="27" t="n"/>
+      <c r="G202" s="27" t="n"/>
+      <c r="H202" s="27" t="n"/>
+      <c r="I202" s="28" t="n">
+        <v>3665.05</v>
+      </c>
+      <c r="J202" s="27" t="n"/>
+      <c r="K202" s="28" t="n">
+        <v>4331949.738327078</v>
       </c>
     </row>
   </sheetData>
